--- a/data/trans_orig/IQ2601_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>31726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49339</t>
+          <t>48562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65235</t>
+          <t>66947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90621</t>
+          <t>90346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90450</t>
+          <t>90299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>49854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>73933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99695</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61340</t>
+          <t>62667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82101</t>
+          <t>82932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87390</t>
+          <t>86691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110066</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155714</t>
+          <t>155878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188555</t>
+          <t>187606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40742</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74423</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99759</t>
+          <t>101095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40187</t>
+          <t>40384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81437</t>
+          <t>79992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107722</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>70485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>87355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>74985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93296</t>
+          <t>93623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>149243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175530</t>
+          <t>175758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63782</t>
+          <t>62919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48715</t>
+          <t>48887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80601</t>
+          <t>80538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>105225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83553</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107691</t>
+          <t>107763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169320</t>
+          <t>169160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203406</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>41363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63626</t>
+          <t>63654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36107</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83674</t>
+          <t>84278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112467</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50253</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31319</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>49497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67757</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93481</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36347</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>261211</t>
+          <t>263129</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>303026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296275</t>
+          <t>293491</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>338652</t>
+          <t>336796</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>570991</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>624687</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151083</t>
+          <t>150806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187087</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129510</t>
+          <t>129697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>163974</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>289172</t>
+          <t>289825</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>338419</t>
+          <t>339162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130364</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165276</t>
+          <t>163718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>137187</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>172021</t>
+          <t>172529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>273433</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>324518</t>
+          <t>324213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>42089</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>91076</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122565</t>
+          <t>123160</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>47036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85993</t>
+          <t>86798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>40989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76027</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>27287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>47342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61578</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86696</t>
+          <t>87724</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>42492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>64855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52958</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73526</t>
+          <t>74923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48337</t>
+          <t>47551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69785</t>
+          <t>69523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108251</t>
+          <t>107045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138229</t>
+          <t>136824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35849</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54690</t>
+          <t>52906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>39932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59572</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80944</t>
+          <t>81303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107010</t>
+          <t>108830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91535</t>
+          <t>91963</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>34020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57844</t>
+          <t>58930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77715</t>
+          <t>77631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105170</t>
+          <t>103765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64340</t>
+          <t>64358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94682</t>
+          <t>93674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>119613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48266</t>
+          <t>47679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69757</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40940</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62082</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48823</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>63924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87818</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79680</t>
+          <t>78456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69689</t>
+          <t>69793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108809</t>
+          <t>109207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139193</t>
+          <t>140690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89368</t>
+          <t>89155</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56574</t>
+          <t>56710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43120</t>
+          <t>42390</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>63644</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>83970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114800</t>
+          <t>112171</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27302</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>46077</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,82 +6888,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>41901</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>32297</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>51414</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>25,46%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>77438</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>64148</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>90741</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>22,46%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>41901</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>33174</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>52218</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>77438</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>64852</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>90805</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198018</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239767</t>
+          <t>238785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>186512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230646</t>
+          <t>226925</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398060</t>
+          <t>399688</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>455568</t>
+          <t>456513</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124126</t>
+          <t>125279</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>158175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>132036</t>
+          <t>130322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>165290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>264106</t>
+          <t>266112</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>317496</t>
+          <t>316600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162517</t>
+          <t>163941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>137316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>173432</t>
+          <t>175016</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>278578</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>329837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74126</t>
+          <t>72983</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>83914</t>
+          <t>83515</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115181</t>
+          <t>116044</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>127810</t>
+          <t>125313</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>161043</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135972</t>
+          <t>135304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>172713</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>271298</t>
+          <t>271604</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>325784</t>
+          <t>320847</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>50654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54931</t>
+          <t>53114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70731</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97038</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49462</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>42291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104532</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,47 +8293,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>35437</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>26843</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>46205</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>9,64%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>35437</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>25626</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>45393</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>37577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41277</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63644</t>
+          <t>63416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64342</t>
+          <t>63613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85974</t>
+          <t>84355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69365</t>
+          <t>68546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91918</t>
+          <t>91276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138794</t>
+          <t>137476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171285</t>
+          <t>169952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57353</t>
+          <t>57563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77633</t>
+          <t>79654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122905</t>
+          <t>122719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154259</t>
+          <t>153866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49325</t>
+          <t>49393</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33003</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>51239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>71124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99516</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>45045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83555</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>48445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66565</t>
+          <t>66923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>61630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81989</t>
+          <t>82127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115109</t>
+          <t>115340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>144347</t>
+          <t>143930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67636</t>
+          <t>67280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91730</t>
+          <t>92637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57614</t>
+          <t>59288</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>81184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58659</t>
+          <t>58630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>80942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122902</t>
+          <t>123635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154917</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72908</t>
+          <t>73871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>61123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97449</t>
+          <t>98398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128829</t>
+          <t>127204</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35665</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39427</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36468</t>
+          <t>35536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58101</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>36703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>57050</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79270</t>
+          <t>78458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>107486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>197221</t>
+          <t>198697</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>236519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208469</t>
+          <t>209137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>250688</t>
+          <t>251510</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>420693</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>476349</t>
+          <t>476569</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>206087</t>
+          <t>207022</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247265</t>
+          <t>247665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>223911</t>
+          <t>224556</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>267559</t>
+          <t>268805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>441092</t>
+          <t>443165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>498702</t>
+          <t>502193</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53445</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>78897</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>101918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>134649</t>
+          <t>134000</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>171386</t>
+          <t>171541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>40627</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142822</t>
+          <t>142533</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>178356</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>131632</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>166683</t>
+          <t>166543</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>282618</t>
+          <t>282595</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>334049</t>
+          <t>333341</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64309</t>
+          <t>64447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>423</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>26872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>45543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>63218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78612</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107942</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76884</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104283</t>
+          <t>103316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>130084</t>
+          <t>130279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>164177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55141</t>
+          <t>55992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
